--- a/dados/EstatisticasDosJogadores.xlsx
+++ b/dados/EstatisticasDosJogadores.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Jogador</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Partidas</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Gols</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Assistências</t>
         </is>
@@ -458,80 +446,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Giorgian De Arrascaeta</t>
+          <t>Carlos Vinícius</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pablo Vegetti</t>
+          <t>Danilo dos Santos de Oliveira</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pedro Raul</t>
+          <t>Vítor Roque</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yuri Alberto</t>
+          <t>Luciano Acosta</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -540,59 +524,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kaio Jorge</t>
+          <t>Jonathan Calleri</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Reinaldo</t>
+          <t>Breno Lopes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>José Manuel López</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -601,96 +583,98 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Memphis Depay</t>
+          <t>Victor Hugo Gomes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ferreira</t>
+          <t>Juninho Capixaba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gabriel Barbosa</t>
+          <t>Walter Clar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rony</t>
+          <t>Jean Carlos</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gabriel Taliari</t>
+          <t>Jean Lucas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -700,12 +684,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Álvaro Barreal</t>
+          <t>Luciano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -714,40 +698,44 @@
       <c r="D14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marllon</t>
+          <t>Alef Manga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Clube do Remo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ignacio Laquintana</t>
+          <t>Igor Formiga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -757,37 +745,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Igor Jesus</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Isidro Pitta</t>
+          <t>Gustavo Gómez</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -797,37 +783,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alan Patrick</t>
+          <t>Allan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rafael Borré</t>
+          <t>John Kennedy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
@@ -837,16 +821,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>José Manuel López</t>
+          <t>Matheus Pereira</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -856,16 +840,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Joaquín Piquerez</t>
+          <t>Negueba</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
@@ -875,37 +859,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Eduardo Sasha</t>
+          <t>Julimar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paranaense</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Matheuzinho</t>
+          <t>Neymar</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
@@ -915,80 +897,76 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jefferson Savarino</t>
+          <t>Gabriel Barbosa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>André Silva</t>
+          <t>Stiven Mendoza</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Paranaense</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daniel Borges</t>
+          <t>Renato Kayzer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Facundo Torres Pérez</t>
+          <t>Gabriel Baralhas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -997,19 +975,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enmerson Batalla</t>
+          <t>Nonato</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -1018,31 +996,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Victor Gabriel</t>
+          <t>Gabriel Menino</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dudu</t>
+          <t>Álvaro Barreal</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1056,58 +1034,54 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lucas Ramon</t>
+          <t>Higor Meritao</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Matías Arezo</t>
+          <t>Rafael Carvalheira</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Edenilson</t>
+          <t>Bidon</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -1117,35 +1091,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Juan Lucero</t>
+          <t>Willian José</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tinga</t>
+          <t>Gonzalo Plata</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
         <v>1</v>
@@ -1155,16 +1131,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Danielzinho</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -1174,16 +1150,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Léo Pereira</t>
+          <t>Philippe Coutinho</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -1193,37 +1169,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nuno Moreira</t>
+          <t>Carlos Eduardo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gilberto</t>
+          <t>Matheus Martins</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
@@ -1233,16 +1207,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Héctor Hernández</t>
+          <t>Artur Guimaraes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
@@ -1252,7 +1226,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eric Ramires</t>
+          <t>Gustavinho</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1261,7 +1235,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
@@ -1271,37 +1245,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Matheus Araújo</t>
+          <t>Rafael Borré</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mateo Ponte</t>
+          <t>Giorgian De Arrascaeta</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
@@ -1311,16 +1283,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>João Pedro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Clube do Remo</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
@@ -1330,75 +1302,77 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Martinelli</t>
+          <t>Zé Rafael</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Leandro Martínez</t>
+          <t>Arthur Cabral</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cristian Renato</t>
+          <t>Tetê</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enner Valencia</t>
+          <t>Edenilson</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
@@ -1408,12 +1382,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wellington Rato</t>
+          <t>Murilo Cerqueira</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1422,21 +1396,23 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Mauricio</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
@@ -1446,16 +1422,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Chrystian Barletta</t>
+          <t>Dudu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -1465,16 +1441,16 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Erick</t>
+          <t>Ramón Sosa</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
@@ -1484,16 +1460,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Thaciano</t>
+          <t>Cristian Olivera</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -1503,56 +1479,56 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Diego Pituca</t>
+          <t>José Rodríguez</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Luciano Juba</t>
+          <t>Joaquín Lavega</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="n">
-        <v>3</v>
-      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Aylon</t>
+          <t>Erick Pulgar</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -1562,31 +1538,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Luiz Mandaca</t>
+          <t>Éverton</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Matheus Babi</t>
+          <t>Matheuzinho</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1600,16 +1578,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Emiliano Martínez</t>
+          <t>Pedro Rocha</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
@@ -1619,37 +1597,35 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Rayan</t>
+          <t>Eduardo Doma</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="n">
-        <v>1</v>
-      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Rubens Tadeu</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
@@ -1659,37 +1635,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Erick</t>
+          <t>Wanderson</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
-      <c r="E63" t="n">
-        <v>1</v>
-      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Samuel Xavier</t>
+          <t>Kaio Jorge</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
@@ -1699,35 +1673,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lucas Halter</t>
+          <t>Hulk</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fausto Vera</t>
+          <t>Vitor Bueno</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Clube do Remo</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
@@ -1737,7 +1713,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Igor Gomes</t>
+          <t>Ruan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1746,7 +1722,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -1756,12 +1732,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Martin Braithwaite</t>
+          <t>Yago Pikachu</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Clube do Remo</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1775,16 +1751,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Juninho Capixaba</t>
+          <t>Dudu</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
@@ -1794,56 +1770,56 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Renê</t>
+          <t>Lucas Moura</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jhon Arias</t>
+          <t>Luciano Juba</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="E71" t="n">
-        <v>3</v>
-      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Erick Pulgar</t>
+          <t>Thaciano</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
@@ -1853,31 +1829,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Gonzalo Plata</t>
+          <t>Kevin Viveros</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Paranaense</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Gabriel Paulista</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1891,16 +1869,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Zé Ivaldo</t>
+          <t>Bidu</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -1910,16 +1888,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Janderson Costa</t>
+          <t>Ronaldo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
@@ -1929,54 +1907,58 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Diogo Barbosa</t>
+          <t>Andreas Pereira</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Lucas Romero</t>
+          <t>Rodrigo Garro</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sergio Oliveira</t>
+          <t>Alan Patrick</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -1986,117 +1968,115 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ênio</t>
+          <t>Leonel Picco</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Clube do Remo</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
-      <c r="E80" t="n">
-        <v>1</v>
-      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Iury</t>
+          <t>Cauly</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="E81" t="n">
-        <v>1</v>
-      </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tiquinho Soares</t>
+          <t>João Pedro</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
       </c>
-      <c r="E82" t="n">
-        <v>1</v>
-      </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tomás Cuello</t>
+          <t>Erick Noriega</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Germán Cano</t>
+          <t>Marlon</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
         <v>1</v>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lucas Braga</t>
+          <t>Cauan Lucas</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
@@ -2106,16 +2086,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Deyverson</t>
+          <t>Tomás Cuello</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
@@ -2125,37 +2105,35 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jhonatan</t>
+          <t>Ramon</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
-      <c r="E87" t="n">
-        <v>1</v>
-      </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Éverton Ribeiro</t>
+          <t>Jacy Maranhão</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -2165,16 +2143,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Edson Carioca</t>
+          <t>Lucas Ronier</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
@@ -2186,16 +2164,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Hulk</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -2207,16 +2185,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Pedro Henrique</t>
+          <t>Jorge Carrascal</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
@@ -2226,16 +2204,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ryan Rodrigues</t>
+          <t>Agustín Canobbio</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -2245,16 +2223,16 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vitinho</t>
+          <t>Thiago Mendes</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
@@ -2264,314 +2242,21 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Éverton</t>
+          <t>Cuiabano</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Kayky</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>7</v>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>5</v>
-      </c>
-      <c r="D96" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Jemerson</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>7</v>
-      </c>
-      <c r="D97" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Carlinhos</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>4</v>
-      </c>
-      <c r="D98" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Deivid Washington</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>7</v>
-      </c>
-      <c r="D99" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Pablo Felipe</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Sport</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>4</v>
-      </c>
-      <c r="D100" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Kevin Serna</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>7</v>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Everaldo</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>7</v>
-      </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Braian Aguirre</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>7</v>
-      </c>
-      <c r="D103" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Thiago Maia</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>7</v>
-      </c>
-      <c r="D104" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Igor Coronado</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Corinthians</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>4</v>
-      </c>
-      <c r="D105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Cauly</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>7</v>
-      </c>
-      <c r="D106" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Vítor Roque</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>7</v>
-      </c>
-      <c r="D107" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Cristian Olivera</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>4</v>
-      </c>
-      <c r="D108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Gustavo Scarpa</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>7</v>
-      </c>
-      <c r="D109" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" t="n">
-        <v>1</v>
-      </c>
+      <c r="E94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
